--- a/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re84a9d28edc049dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R34fc8948476c490b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R34fc8948476c490b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7be35ad1a5ba4dd1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7be35ad1a5ba4dd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R451caa008cb54480"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R451caa008cb54480"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1ab7a73da03d4545"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1ab7a73da03d4545"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfcf88708ef3d43fb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfcf88708ef3d43fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R770ee182a40d4b5b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R770ee182a40d4b5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R562bf148ca1342df"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R562bf148ca1342df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd25c03c79a32423c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd25c03c79a32423c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R06b183c9200d42b3"/>
   </x:sheets>
 </x:workbook>
 </file>
